--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfsoa\Desktop\Nutri_Hospital\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfsoa\Desktop\Apps\db_nutribody\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A701B980-2D47-48DC-882E-2CFEFBEFD7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25AC8A36-0D11-407E-BA87-C537D6EBBE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38490" yWindow="60" windowWidth="19020" windowHeight="15600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="2" xr2:uid="{334EDE72-1191-41F7-AA76-F0137DE60740}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODIET" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="DANONE" sheetId="3" r:id="rId3"/>
     <sheet name="FRESENIUS" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="191">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -213,18 +213,6 @@
     <t>TROPHIC BASIC</t>
   </si>
   <si>
-    <t>TROPHIC BASIC (RTH E SA)</t>
-  </si>
-  <si>
-    <t>400/800/2,07G</t>
-  </si>
-  <si>
-    <t>TROPHIC 1.5 (RTH/SA)</t>
-  </si>
-  <si>
-    <t>1000ML E 250ML</t>
-  </si>
-  <si>
     <t>TROPHIC EP</t>
   </si>
   <si>
@@ -243,9 +231,6 @@
     <t>TROPHIC JUNIOR</t>
   </si>
   <si>
-    <t>370/740G</t>
-  </si>
-  <si>
     <t>ENERGYZIP SENIOR</t>
   </si>
   <si>
@@ -279,9 +264,6 @@
     <t xml:space="preserve">DIAMAX IG </t>
   </si>
   <si>
-    <t>1000ML/200ML</t>
-  </si>
-  <si>
     <t>DIAMAX IN</t>
   </si>
   <si>
@@ -300,21 +282,9 @@
     <t>ENTERFIBER PREBIOTIC (FIBRAS SOLUVEIS)</t>
   </si>
   <si>
-    <t>400G/25G</t>
-  </si>
-  <si>
     <t>CARBO CH</t>
   </si>
   <si>
-    <t>INSTANTH CLEAR (TEXTURA NECTAR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                     TEXTURA MEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                     TEXTURA PUDIM</t>
-  </si>
-  <si>
     <t>ENERGYZIP SUSLAC</t>
   </si>
   <si>
@@ -438,19 +408,22 @@
     <t>1G</t>
   </si>
   <si>
-    <t>2G</t>
-  </si>
-  <si>
-    <t>3G</t>
-  </si>
-  <si>
     <t>GORDURA SATURADA (g)</t>
   </si>
   <si>
     <t>NUTRISON ADVANCE DIASON ENERGY HP</t>
   </si>
   <si>
-    <t>Produto</t>
+    <t>DIBEN</t>
+  </si>
+  <si>
+    <t>GORDURA SATURADA (g/L)</t>
+  </si>
+  <si>
+    <t>FRESUBIN ENERGY DRINK</t>
+  </si>
+  <si>
+    <t>SURVIMED OPD DRINK</t>
   </si>
   <si>
     <t>DIBEN 1.5</t>
@@ -459,42 +432,33 @@
     <t>1000ML/500ML</t>
   </si>
   <si>
-    <t>DIBEN</t>
-  </si>
-  <si>
-    <t>FRESUBIN ENERGY DRINK</t>
-  </si>
-  <si>
-    <t>SURVIMED OPD DRINK</t>
-  </si>
-  <si>
     <t>FEBRINI ENERGY DRINK</t>
   </si>
   <si>
     <t>FEBRINI ENERGY FIBRE</t>
   </si>
   <si>
+    <t>FEBRINI ORIGINAL FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN 1.2 HP FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2 KCAL CREME</t>
+  </si>
+  <si>
+    <t>125G</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2KCAL DRINK</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2KCAL DRINK FIBRE</t>
+  </si>
+  <si>
     <t>FEBRINI ORIGINAL</t>
   </si>
   <si>
-    <t>FEBRINI ORIGINAL FIBRE</t>
-  </si>
-  <si>
-    <t>FRESUBIN 1.2 HP FIBRE</t>
-  </si>
-  <si>
-    <t>FRESUBIN 2 KCAL CREME</t>
-  </si>
-  <si>
-    <t>125G</t>
-  </si>
-  <si>
-    <t>FRESUBIN 2KCAL DRINK</t>
-  </si>
-  <si>
-    <t>FRESUBIN 2KCAL DRINK FIBRE</t>
-  </si>
-  <si>
     <t>FRESUBIN 2KCAL HP FIBRE</t>
   </si>
   <si>
@@ -507,70 +471,136 @@
     <t>FRESUBIN 5KCAL SHOT</t>
   </si>
   <si>
+    <t>FRESUBIN ENERGY FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN ENERGY</t>
+  </si>
+  <si>
+    <t>FRESUBIN HEPA</t>
+  </si>
+  <si>
+    <t>FRESUBIN HP ENERGY FB</t>
+  </si>
+  <si>
+    <t>FRESUBIN JUCY DRINK</t>
+  </si>
+  <si>
+    <t>FRESUBIN LP</t>
+  </si>
+  <si>
+    <t>FRESUBIN PROTEIN ENERGY DRINK</t>
+  </si>
+  <si>
+    <t>FRESUBIN PROTEIN POWDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPPORTAN </t>
+  </si>
+  <si>
+    <t>SUPPORTAN DRINK</t>
+  </si>
+  <si>
+    <t>SURVIMED OPD</t>
+  </si>
+  <si>
+    <t>SURVIMED OPD HN</t>
+  </si>
+  <si>
+    <t>THICK &amp; EASY</t>
+  </si>
+  <si>
+    <t>THICK &amp; EASY CLEAR</t>
+  </si>
+  <si>
+    <t>FRESUBIN PRO DRINK</t>
+  </si>
+  <si>
     <t>120ML</t>
   </si>
   <si>
-    <t>FRESUBIN ENERGY FIBRE</t>
-  </si>
-  <si>
-    <t>FRESUBIN ENERGY</t>
-  </si>
-  <si>
-    <t>FRESUBIN HEPA</t>
-  </si>
-  <si>
-    <t>FRESUBIN HP ENERGY FB</t>
-  </si>
-  <si>
     <t>FRESUBIN HP ENERGY</t>
   </si>
   <si>
-    <t>FRESUBIN JUCY DRINK</t>
-  </si>
-  <si>
-    <t>FRESUBIN LP</t>
-  </si>
-  <si>
-    <t>FRESUBIN PROTEIN ENERGY DRINK</t>
-  </si>
-  <si>
-    <t>FRESUBIN PROTEIN POWDER</t>
-  </si>
-  <si>
     <t>300g</t>
   </si>
   <si>
-    <t xml:space="preserve">SUPPORTAN </t>
-  </si>
-  <si>
-    <t>SUPPORTAN DRINK</t>
-  </si>
-  <si>
-    <t>SURVIMED OPD</t>
-  </si>
-  <si>
     <t>1000ml</t>
   </si>
   <si>
-    <t>SURVIMED OPD HN</t>
-  </si>
-  <si>
     <t>500ml</t>
   </si>
   <si>
-    <t>THICK &amp; EASY</t>
-  </si>
-  <si>
     <t>225G</t>
   </si>
   <si>
-    <t>THICK &amp; EASY CLEAR</t>
-  </si>
-  <si>
     <t>126G</t>
   </si>
   <si>
-    <t>FRESUBIN PRO DRINK</t>
+    <t>TROPHIC 1.5 RTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000ML </t>
+  </si>
+  <si>
+    <t>APRESENTAÇÃO</t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5</t>
+  </si>
+  <si>
+    <t>1.000ML</t>
+  </si>
+  <si>
+    <t>LÍQUIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIQUIDO </t>
+  </si>
+  <si>
+    <t>250ML</t>
+  </si>
+  <si>
+    <t>TROPHIC BASIC RTH</t>
+  </si>
+  <si>
+    <t>800G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100G </t>
+  </si>
+  <si>
+    <t>PÓ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400G </t>
+  </si>
+  <si>
+    <t>2,07KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROPHIC 1.5 FIBER </t>
+  </si>
+  <si>
+    <t>370G</t>
+  </si>
+  <si>
+    <t>740G</t>
+  </si>
+  <si>
+    <t>700G</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>25G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTANTH CLEAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">300G </t>
   </si>
 </sst>
 </file>
@@ -609,18 +639,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -635,7 +659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -646,9 +670,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,9 +688,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -707,9 +728,9 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -761,7 +782,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -813,7 +834,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -955,15 +976,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78DB9DD0-9A75-4AEF-8A0B-8A9789369C22}">
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
@@ -975,9 +996,10 @@
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="14.140625" customWidth="1"/>
     <col min="12" max="12" width="25.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1012,15 +1034,18 @@
         <v>59</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -1052,51 +1077,57 @@
       <c r="L2">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E3">
-        <v>4.5999999999999996</v>
+        <v>5.7</v>
       </c>
       <c r="F3">
-        <v>4.0999999999999996</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J3">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="K3">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="L3">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+      <c r="M3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1105,33 +1136,36 @@
         <v>150</v>
       </c>
       <c r="E4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G4">
-        <v>2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="I4">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J4">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="K4">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+      <c r="M4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1143,74 +1177,80 @@
         <v>150</v>
       </c>
       <c r="E5">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="F5">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H5">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I5">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J5">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="K5">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>435</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>5.8</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H6">
-        <v>265</v>
+        <v>120</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J6">
-        <v>770</v>
+        <v>314</v>
       </c>
       <c r="K6">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1219,33 +1259,36 @@
         <v>150</v>
       </c>
       <c r="E7">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H7">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J7">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="K7">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="L7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1254,36 +1297,39 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E8">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>91</v>
+      </c>
+      <c r="I8">
         <v>2</v>
       </c>
-      <c r="H8">
-        <v>64</v>
-      </c>
-      <c r="I8">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="J8">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="K8">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="L8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+      <c r="M8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1298,817 +1344,1586 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="F9">
-        <v>3.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="I9">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="K9">
-        <v>0.52</v>
+        <v>0.24</v>
       </c>
       <c r="L9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.6</v>
+      </c>
+      <c r="M9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10">
+        <v>435</v>
+      </c>
+      <c r="E10">
+        <v>16</v>
+      </c>
+      <c r="F10">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10">
-        <v>150</v>
-      </c>
-      <c r="E10">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>265</v>
+      </c>
+      <c r="I10">
         <v>5</v>
       </c>
-      <c r="F10">
-        <v>5.7</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>91</v>
-      </c>
-      <c r="I10">
+      <c r="J10">
+        <v>770</v>
+      </c>
+      <c r="K10">
+        <v>1.3</v>
+      </c>
+      <c r="L10">
         <v>2</v>
       </c>
-      <c r="J10">
-        <v>300</v>
-      </c>
-      <c r="K10">
-        <v>0.45</v>
-      </c>
-      <c r="L10">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>150</v>
+        <v>435</v>
       </c>
       <c r="E11">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>5.0999999999999996</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>142</v>
+        <v>265</v>
       </c>
       <c r="I11">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>240</v>
+        <v>770</v>
       </c>
       <c r="K11">
-        <v>0.28000000000000003</v>
+        <v>1.3</v>
       </c>
       <c r="L11">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="M11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>150</v>
+        <v>435</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F12">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>265</v>
+      </c>
+      <c r="I12">
         <v>5</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>242</v>
-      </c>
-      <c r="I12">
-        <v>4.2</v>
-      </c>
       <c r="J12">
-        <v>540</v>
+        <v>770</v>
       </c>
       <c r="K12">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="L12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+      <c r="E13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F13">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>44</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>204</v>
+      </c>
+      <c r="K13">
+        <v>0.24</v>
+      </c>
+      <c r="L13">
+        <v>0.6</v>
+      </c>
+      <c r="M13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>150</v>
+      </c>
+      <c r="E14">
+        <v>7.6</v>
+      </c>
+      <c r="F14">
+        <v>5.7</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>123</v>
+      </c>
+      <c r="I14">
+        <v>1.5</v>
+      </c>
+      <c r="J14">
+        <v>307</v>
+      </c>
+      <c r="K14">
+        <v>0.46</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>150</v>
+      </c>
+      <c r="E15">
+        <v>6.9</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>73</v>
+      </c>
+      <c r="I15">
+        <v>1.5</v>
+      </c>
+      <c r="J15">
+        <v>257</v>
+      </c>
+      <c r="K15">
+        <v>0.32</v>
+      </c>
+      <c r="L15">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>120</v>
+      </c>
+      <c r="E16">
+        <v>4.5</v>
+      </c>
+      <c r="F16">
+        <v>3.9</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>64</v>
+      </c>
+      <c r="I16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J16">
+        <v>235</v>
+      </c>
+      <c r="K16">
+        <v>0.2</v>
+      </c>
+      <c r="L16">
+        <v>0.5</v>
+      </c>
+      <c r="M16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C17" t="s">
         <v>9</v>
       </c>
-      <c r="D13">
-        <v>461</v>
-      </c>
-      <c r="E13">
-        <v>14</v>
-      </c>
-      <c r="F13">
-        <v>176</v>
-      </c>
-      <c r="G13">
-        <v>17</v>
-      </c>
-      <c r="H13">
-        <v>266</v>
-      </c>
-      <c r="I13">
-        <v>5</v>
-      </c>
-      <c r="J13">
-        <v>739</v>
-      </c>
-      <c r="K13">
-        <v>77</v>
-      </c>
-      <c r="L13">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14">
-        <v>222</v>
-      </c>
-      <c r="E14">
-        <v>14</v>
-      </c>
-      <c r="F14">
-        <v>7.4</v>
-      </c>
-      <c r="G14">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H14">
-        <v>107</v>
-      </c>
-      <c r="I14">
-        <v>3</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>1.7</v>
-      </c>
-      <c r="L14">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
       <c r="D17">
-        <v>199.97</v>
+        <v>120</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="G17">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="K17">
-        <v>2.2999999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="M17" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>393</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="F18">
+        <v>3.9</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>64</v>
+      </c>
+      <c r="I18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J18">
+        <v>235</v>
+      </c>
+      <c r="K18">
+        <v>0.2</v>
+      </c>
+      <c r="L18">
+        <v>0.5</v>
+      </c>
+      <c r="M18" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" t="s">
         <v>9</v>
       </c>
-      <c r="G18">
-        <v>6</v>
-      </c>
-      <c r="H18">
-        <v>259</v>
-      </c>
-      <c r="I18">
-        <v>3.4</v>
-      </c>
-      <c r="J18">
-        <v>750</v>
-      </c>
-      <c r="K18">
-        <v>1.4</v>
-      </c>
-      <c r="L18">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
       <c r="D19">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E19">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F19">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="G19">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>6.7</v>
+        <v>64</v>
       </c>
       <c r="I19">
         <v>1.1000000000000001</v>
       </c>
       <c r="J19">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="K19">
-        <v>0.14000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="L19">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D20">
-        <v>239</v>
+        <v>120</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F20">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="G20">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="K20">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="L20">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.4</v>
+      </c>
+      <c r="M20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E21">
-        <v>6.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F21">
-        <v>4.5999999999999996</v>
+        <v>3.9</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="I21">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J21">
-        <v>60</v>
+        <v>232</v>
       </c>
       <c r="K21">
-        <v>0.55000000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="L21">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.4</v>
+      </c>
+      <c r="M21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22">
-        <v>406</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>275</v>
+        <v>103</v>
       </c>
       <c r="I22">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J22">
-        <v>836</v>
+        <v>232</v>
       </c>
       <c r="K22">
-        <v>0.91</v>
+        <v>0.52</v>
       </c>
       <c r="L22">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.4</v>
+      </c>
+      <c r="M22" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>103</v>
+      </c>
+      <c r="I23">
+        <v>2.7</v>
+      </c>
+      <c r="J23">
+        <v>232</v>
+      </c>
+      <c r="K23">
+        <v>0.52</v>
+      </c>
+      <c r="L23">
+        <v>0.4</v>
+      </c>
+      <c r="M23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>150</v>
+      </c>
+      <c r="E24">
+        <v>5.7</v>
+      </c>
+      <c r="F24">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>142</v>
+      </c>
+      <c r="I24">
+        <v>1.7</v>
+      </c>
+      <c r="J24">
+        <v>240</v>
+      </c>
+      <c r="K24">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L24">
+        <v>0.7</v>
+      </c>
+      <c r="M24" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>150</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>242</v>
+      </c>
+      <c r="I25">
+        <v>4.2</v>
+      </c>
+      <c r="J25">
+        <v>540</v>
+      </c>
+      <c r="K25">
+        <v>0.9</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>461</v>
+      </c>
+      <c r="E26">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>176</v>
+      </c>
+      <c r="G26">
+        <v>17</v>
+      </c>
+      <c r="H26">
+        <v>266</v>
+      </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
+      <c r="J26">
+        <v>739</v>
+      </c>
+      <c r="K26">
+        <v>77</v>
+      </c>
+      <c r="L26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>461</v>
+      </c>
+      <c r="E27">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>176</v>
+      </c>
+      <c r="G27">
+        <v>17</v>
+      </c>
+      <c r="H27">
+        <v>266</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
+        <v>739</v>
+      </c>
+      <c r="K27">
+        <v>77</v>
+      </c>
+      <c r="L27">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28">
+        <v>222</v>
+      </c>
+      <c r="E28">
+        <v>14</v>
+      </c>
+      <c r="F28">
+        <v>7.4</v>
+      </c>
+      <c r="G28">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H28">
+        <v>107</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1.7</v>
+      </c>
+      <c r="L28">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29">
+        <v>222</v>
+      </c>
+      <c r="E29">
+        <v>14</v>
+      </c>
+      <c r="F29">
+        <v>7.4</v>
+      </c>
+      <c r="G29">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H29">
+        <v>107</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1.7</v>
+      </c>
+      <c r="L29">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
         <v>100</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32">
+        <v>199.97</v>
+      </c>
+      <c r="E32">
+        <v>25</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>3.2</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <v>393</v>
+      </c>
+      <c r="E33">
+        <v>25</v>
+      </c>
+      <c r="F33">
+        <v>9</v>
+      </c>
+      <c r="G33">
+        <v>6</v>
+      </c>
+      <c r="H33">
+        <v>259</v>
+      </c>
+      <c r="I33">
+        <v>3.4</v>
+      </c>
+      <c r="J33">
+        <v>750</v>
+      </c>
+      <c r="K33">
+        <v>1.4</v>
+      </c>
+      <c r="L33">
+        <v>1.6</v>
+      </c>
+      <c r="M33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34">
+        <v>393</v>
+      </c>
+      <c r="E34">
+        <v>25</v>
+      </c>
+      <c r="F34">
+        <v>9</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34">
+        <v>259</v>
+      </c>
+      <c r="I34">
+        <v>3.4</v>
+      </c>
+      <c r="J34">
+        <v>750</v>
+      </c>
+      <c r="K34">
+        <v>1.4</v>
+      </c>
+      <c r="L34">
+        <v>1.6</v>
+      </c>
+      <c r="M34" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35">
+        <v>100</v>
+      </c>
+      <c r="E35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F35">
+        <v>4.7</v>
+      </c>
+      <c r="G35">
+        <v>1.5</v>
+      </c>
+      <c r="H35">
+        <v>6.7</v>
+      </c>
+      <c r="I35">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J35">
+        <v>136</v>
+      </c>
+      <c r="K35">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L35">
+        <v>0.5</v>
+      </c>
+      <c r="M35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
+      </c>
+      <c r="E36">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F36">
+        <v>4.7</v>
+      </c>
+      <c r="G36">
+        <v>1.5</v>
+      </c>
+      <c r="H36">
+        <v>6.7</v>
+      </c>
+      <c r="I36">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J36">
+        <v>136</v>
+      </c>
+      <c r="K36">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L36">
+        <v>0.5</v>
+      </c>
+      <c r="M36" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37">
+        <v>239</v>
+      </c>
+      <c r="E37">
+        <v>15</v>
+      </c>
+      <c r="F37">
+        <v>9.4</v>
+      </c>
+      <c r="G37">
+        <v>3.1</v>
+      </c>
+      <c r="H37">
+        <v>126</v>
+      </c>
+      <c r="I37">
+        <v>3.5</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0.3</v>
+      </c>
+      <c r="L37">
+        <v>9.4</v>
+      </c>
+      <c r="M37" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38">
+        <v>239</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
+      </c>
+      <c r="F38">
+        <v>9.4</v>
+      </c>
+      <c r="G38">
+        <v>3.1</v>
+      </c>
+      <c r="H38">
+        <v>126</v>
+      </c>
+      <c r="I38">
+        <v>3.5</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0.3</v>
+      </c>
+      <c r="L38">
+        <v>9.4</v>
+      </c>
+      <c r="M38" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39">
+        <v>150</v>
+      </c>
+      <c r="E39">
+        <v>6.7</v>
+      </c>
+      <c r="F39">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>115</v>
+      </c>
+      <c r="I39">
+        <v>1.3</v>
+      </c>
+      <c r="J39">
+        <v>60</v>
+      </c>
+      <c r="K39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L39">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M39" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40">
+        <v>406</v>
+      </c>
+      <c r="E40">
+        <v>18</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>275</v>
+      </c>
+      <c r="I40">
+        <v>3.1</v>
+      </c>
+      <c r="J40">
+        <v>836</v>
+      </c>
+      <c r="K40">
+        <v>0.91</v>
+      </c>
+      <c r="L40">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>188</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43">
+        <v>100</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44">
+        <v>100</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>189</v>
+      </c>
+      <c r="B45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C45" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0.2</v>
+      </c>
+      <c r="H45">
+        <v>2.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46">
+        <v>224</v>
+      </c>
+      <c r="E46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46">
+        <v>0.72</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>83</v>
+      </c>
+      <c r="I46">
+        <v>9</v>
+      </c>
+      <c r="J46">
+        <v>30</v>
+      </c>
+      <c r="K46">
+        <v>4</v>
+      </c>
+      <c r="L46">
+        <v>0.48</v>
+      </c>
+      <c r="M46" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" t="s">
         <v>89</v>
       </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>100</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25">
-        <v>100</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26">
-        <v>125</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="I26" s="6">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6">
-        <v>0</v>
-      </c>
-      <c r="K26" s="6">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>32</v>
+      </c>
+      <c r="E47">
         <v>7</v>
       </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="H27" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="I27" s="6">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6">
-        <v>0</v>
-      </c>
-      <c r="K27" s="6">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D28" s="6">
-        <v>15</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="H28" s="6">
-        <v>11</v>
-      </c>
-      <c r="I28" s="6">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6">
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
-        <v>0</v>
-      </c>
-      <c r="L28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29">
-        <v>224</v>
-      </c>
-      <c r="E29" t="s">
-        <v>97</v>
-      </c>
-      <c r="F29">
-        <v>0.72</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>83</v>
-      </c>
-      <c r="I29">
-        <v>9</v>
-      </c>
-      <c r="J29">
-        <v>30</v>
-      </c>
-      <c r="K29">
-        <v>4</v>
-      </c>
-      <c r="L29" s="6">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-      <c r="D30">
-        <v>32</v>
-      </c>
-      <c r="E30">
-        <v>7</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>14</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30" s="6">
-        <v>0</v>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2117,7 +2932,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2123C72-4A12-47A7-AB61-5C3231F6816A}">
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2166,7 +2981,7 @@
         <v>6</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2475,7 +3290,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -2589,7 +3404,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -2627,7 +3442,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -3350,7 +4165,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78691312-69DB-4659-B4D6-AEC80D68ABAB}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3367,7 +4182,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>58</v>
@@ -3400,12 +4215,12 @@
         <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
@@ -3443,7 +4258,7 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -3481,10 +4296,10 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3519,7 +4334,7 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -3557,7 +4372,7 @@
     </row>
     <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -3595,7 +4410,7 @@
     </row>
     <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -3633,7 +4448,7 @@
     </row>
     <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -3671,7 +4486,7 @@
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -3709,7 +4524,7 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -3747,7 +4562,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -3782,7 +4597,7 @@
     </row>
     <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -3820,7 +4635,7 @@
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -3858,7 +4673,7 @@
     </row>
     <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -3896,10 +4711,10 @@
     </row>
     <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -3934,10 +4749,10 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
@@ -3972,10 +4787,10 @@
     </row>
     <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
@@ -4010,13 +4825,13 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D18">
         <v>111</v>
@@ -4048,7 +4863,7 @@
     </row>
     <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -4086,7 +4901,7 @@
     </row>
     <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -4124,7 +4939,7 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -4162,13 +4977,13 @@
     </row>
     <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D22">
         <v>42</v>
@@ -4203,7 +5018,7 @@
         <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D23">
         <v>56</v>
@@ -4238,7 +5053,7 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D24">
         <v>70</v>
@@ -4274,21 +5089,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21AC3A0D-9B40-464F-BF54-D59F81C185B7}">
   <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -4326,1258 +5139,1257 @@
         <v>59</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>150</v>
+      </c>
+      <c r="E2" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="F2" s="4">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H2" s="4">
+        <v>55</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>180</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G3">
+        <v>1.5</v>
+      </c>
+      <c r="H3">
+        <v>85</v>
+      </c>
+      <c r="I3">
+        <v>1.5</v>
+      </c>
+      <c r="J3">
+        <v>143</v>
+      </c>
+      <c r="K3">
+        <v>0.3</v>
+      </c>
+      <c r="L3">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <v>56</v>
+      </c>
+      <c r="F4">
+        <v>58</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>80</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>135</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>47</v>
+      </c>
+      <c r="F5">
+        <v>28</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>80</v>
+      </c>
+      <c r="J5">
+        <v>200</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+      <c r="E6">
+        <v>3.8</v>
+      </c>
+      <c r="F6">
+        <v>6.7</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>81</v>
+      </c>
+      <c r="I6">
+        <v>1.5</v>
+      </c>
+      <c r="J6">
+        <v>150</v>
+      </c>
+      <c r="K6">
+        <v>0.3</v>
+      </c>
+      <c r="L6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <v>3.8</v>
+      </c>
+      <c r="F7">
+        <v>6.7</v>
+      </c>
+      <c r="G7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H7">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>1.5</v>
+      </c>
+      <c r="J7">
+        <v>150</v>
+      </c>
+      <c r="K7">
+        <v>0.54</v>
+      </c>
+      <c r="L7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>2.5</v>
+      </c>
+      <c r="F8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>54</v>
+      </c>
+      <c r="I8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>0.25</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>2.5</v>
+      </c>
+      <c r="F9">
+        <v>4.45</v>
+      </c>
+      <c r="G9">
+        <v>0.8</v>
+      </c>
+      <c r="H9">
+        <v>54</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>0.2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>120</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>115</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>223</v>
+      </c>
+      <c r="K10">
+        <v>0.7</v>
+      </c>
+      <c r="L10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="B11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>200</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>7.8</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>65</v>
+      </c>
+      <c r="I11">
+        <v>2.5</v>
+      </c>
+      <c r="J11">
+        <v>167</v>
+      </c>
+      <c r="K11">
+        <v>0.88</v>
+      </c>
+      <c r="L11">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>200</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>7.8</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>60</v>
+      </c>
+      <c r="I12">
+        <v>2.5</v>
+      </c>
+      <c r="J12">
+        <v>160</v>
+      </c>
+      <c r="K12">
+        <v>0.64</v>
+      </c>
+      <c r="L12">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>200</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>7.8</v>
+      </c>
+      <c r="G13">
+        <v>1.6</v>
+      </c>
+      <c r="H13">
+        <v>60</v>
+      </c>
+      <c r="I13">
+        <v>2.5</v>
+      </c>
+      <c r="J13">
+        <v>160</v>
+      </c>
+      <c r="K13">
+        <v>0.64</v>
+      </c>
+      <c r="L13">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1.5</v>
+      </c>
+      <c r="H14">
+        <v>60</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>170</v>
+      </c>
+      <c r="K14">
+        <v>0.85</v>
+      </c>
+      <c r="L14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>200</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>60</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <v>170</v>
+      </c>
+      <c r="K15">
+        <v>0.75</v>
+      </c>
+      <c r="L15">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>320</v>
+      </c>
+      <c r="E16">
+        <v>16</v>
+      </c>
+      <c r="F16">
+        <v>16</v>
+      </c>
+      <c r="G16">
+        <v>0.5</v>
+      </c>
+      <c r="H16">
+        <v>112</v>
+      </c>
+      <c r="I16">
+        <v>4.8</v>
+      </c>
+      <c r="J16">
+        <v>312</v>
+      </c>
+      <c r="K16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L16">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>500</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>53.8</v>
+      </c>
+      <c r="G17">
+        <v>0.4</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18">
         <v>150</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E18">
+        <v>5.6</v>
+      </c>
+      <c r="F18">
+        <v>5.8</v>
+      </c>
+      <c r="G18">
+        <v>150</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>1.45</v>
+      </c>
+      <c r="J18">
+        <v>200</v>
+      </c>
+      <c r="K18">
+        <v>0.37</v>
+      </c>
+      <c r="L18">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>150</v>
+      </c>
+      <c r="E19">
+        <v>5.6</v>
+      </c>
+      <c r="F19">
+        <v>5.8</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <v>1.4</v>
+      </c>
+      <c r="J19">
+        <v>200</v>
+      </c>
+      <c r="K19">
+        <v>0.35</v>
+      </c>
+      <c r="L19">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>130</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>4.7</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>75</v>
+      </c>
+      <c r="I20">
+        <v>1.33</v>
+      </c>
+      <c r="J20">
+        <v>120</v>
+      </c>
+      <c r="K20">
+        <v>0.27</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>150</v>
+      </c>
+      <c r="E21">
         <v>7.5</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F21">
+        <v>5.8</v>
+      </c>
+      <c r="G21">
+        <v>1.5</v>
+      </c>
+      <c r="H21">
+        <v>95</v>
+      </c>
+      <c r="I21">
+        <v>1.33</v>
+      </c>
+      <c r="J21">
+        <v>234</v>
+      </c>
+      <c r="K21">
+        <v>0.27</v>
+      </c>
+      <c r="L21">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>150</v>
+      </c>
+      <c r="E22">
+        <v>7.5</v>
+      </c>
+      <c r="F22">
+        <v>5.8</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>120</v>
+      </c>
+      <c r="I22">
+        <v>1.33</v>
+      </c>
+      <c r="J22">
+        <v>234</v>
+      </c>
+      <c r="K22">
+        <v>0.3</v>
+      </c>
+      <c r="L22">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23">
+        <v>150</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>2.5</v>
+      </c>
+      <c r="J23">
         <v>7</v>
       </c>
-      <c r="G2" s="8">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="H2" s="8">
-        <v>55</v>
-      </c>
-      <c r="I2" s="8">
+      <c r="K23">
+        <v>0.75</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>200</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>8.9</v>
+      </c>
+      <c r="G24">
+        <v>1.2</v>
+      </c>
+      <c r="H24">
+        <v>68</v>
+      </c>
+      <c r="I24">
         <v>2</v>
       </c>
-      <c r="J2" s="8">
-        <v>180</v>
-      </c>
-      <c r="K2" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="L2" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>0.6</v>
+      </c>
+      <c r="L24">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>150</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>6.7</v>
+      </c>
+      <c r="G25">
+        <v>0.5</v>
+      </c>
+      <c r="H25">
+        <v>58</v>
+      </c>
+      <c r="I25">
+        <v>2.5</v>
+      </c>
+      <c r="J25">
+        <v>146</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>360</v>
+      </c>
+      <c r="E26">
+        <v>87</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>550</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1200</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>150</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>6.7</v>
+      </c>
+      <c r="G27">
+        <v>1.2</v>
+      </c>
+      <c r="H27">
+        <v>47.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>128</v>
+      </c>
+      <c r="K27">
+        <v>0.75</v>
+      </c>
+      <c r="L27">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>150</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>6.7</v>
+      </c>
+      <c r="G28">
+        <v>1.5</v>
+      </c>
+      <c r="H28">
+        <v>50</v>
+      </c>
+      <c r="I28">
+        <v>2.5</v>
+      </c>
+      <c r="J28">
+        <v>146</v>
+      </c>
+      <c r="K28">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L28">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29">
         <v>100</v>
       </c>
-      <c r="E3" s="7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F3" s="7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="H3" s="7">
-        <v>85</v>
-      </c>
-      <c r="I3" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="J3" s="7">
-        <v>143</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="E29">
+        <v>4.5</v>
+      </c>
+      <c r="F29">
+        <v>2.8</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>80</v>
+      </c>
+      <c r="I29">
+        <v>1.4</v>
+      </c>
+      <c r="J29">
+        <v>200</v>
+      </c>
+      <c r="K29">
+        <v>0.45</v>
+      </c>
+      <c r="L29">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F30">
+        <v>2.8</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>80</v>
+      </c>
+      <c r="I30">
+        <v>1.3</v>
+      </c>
+      <c r="J30">
+        <v>200</v>
+      </c>
+      <c r="K30">
+        <v>0.35</v>
+      </c>
+      <c r="L30">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31">
+        <v>133</v>
+      </c>
+      <c r="E31">
+        <v>6.7</v>
+      </c>
+      <c r="F31">
+        <v>3.7</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>135</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>260</v>
+      </c>
+      <c r="K31">
+        <v>0.5</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>373</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>174</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <v>291.10000000000002</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>31.2</v>
+      </c>
+      <c r="H33">
+        <v>1344</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>449</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>161</v>
+      </c>
+      <c r="B34" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7">
-        <v>150</v>
-      </c>
-      <c r="E4" s="7">
-        <v>56</v>
-      </c>
-      <c r="F4" s="7">
-        <v>58</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>80</v>
-      </c>
-      <c r="I4" s="7">
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <v>240</v>
+      </c>
+      <c r="E34">
+        <v>14.4</v>
+      </c>
+      <c r="F34">
+        <v>9.4</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>30</v>
+      </c>
+      <c r="I34">
         <v>2</v>
       </c>
-      <c r="J4" s="7">
-        <v>135</v>
-      </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="7">
-        <v>100</v>
-      </c>
-      <c r="E5" s="7">
-        <v>47</v>
-      </c>
-      <c r="F5" s="7">
-        <v>28</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>80</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7">
-        <v>200</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7">
-        <v>150</v>
-      </c>
-      <c r="E6" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="F6" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
-        <v>81</v>
-      </c>
-      <c r="I6" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="J6" s="7">
-        <v>150</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7">
-        <v>150</v>
-      </c>
-      <c r="E7" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="F7" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="J34">
+        <v>87</v>
+      </c>
+      <c r="K34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H7" s="7">
-        <v>81</v>
-      </c>
-      <c r="I7" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="J7" s="7">
-        <v>150</v>
-      </c>
-      <c r="K7" s="7">
-        <v>0.54</v>
-      </c>
-      <c r="L7" s="7">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="7">
-        <v>100</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="F8" s="7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>54</v>
-      </c>
-      <c r="I8" s="7">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J8" s="7">
-        <v>100</v>
-      </c>
-      <c r="K8" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="L8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="7">
-        <v>100</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="F9" s="7">
-        <v>4.45</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="H9" s="7">
-        <v>54</v>
-      </c>
-      <c r="I9" s="7">
-        <v>1</v>
-      </c>
-      <c r="J9" s="7">
-        <v>100</v>
-      </c>
-      <c r="K9" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="L9" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7">
-        <v>120</v>
-      </c>
-      <c r="E10" s="7">
-        <v>6</v>
-      </c>
-      <c r="F10" s="7">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="G10" s="7">
-        <v>2</v>
-      </c>
-      <c r="H10" s="7">
-        <v>115</v>
-      </c>
-      <c r="I10" s="7">
-        <v>2</v>
-      </c>
-      <c r="J10" s="7">
-        <v>223</v>
-      </c>
-      <c r="K10" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="L10" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="7">
-        <v>200</v>
-      </c>
-      <c r="E11" s="7">
-        <v>10</v>
-      </c>
-      <c r="F11" s="7">
-        <v>7.8</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>65</v>
-      </c>
-      <c r="I11" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="J11" s="7">
-        <v>167</v>
-      </c>
-      <c r="K11" s="7">
-        <v>0.88</v>
-      </c>
-      <c r="L11" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7">
-        <v>200</v>
-      </c>
-      <c r="E12" s="7">
-        <v>10</v>
-      </c>
-      <c r="F12" s="7">
-        <v>7.8</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>60</v>
-      </c>
-      <c r="I12" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="J12" s="7">
-        <v>160</v>
-      </c>
-      <c r="K12" s="7">
-        <v>0.64</v>
-      </c>
-      <c r="L12" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="7">
-        <v>200</v>
-      </c>
-      <c r="E13" s="7">
-        <v>10</v>
-      </c>
-      <c r="F13" s="7">
-        <v>7.8</v>
-      </c>
-      <c r="G13" s="7">
-        <v>1.6</v>
-      </c>
-      <c r="H13" s="7">
-        <v>60</v>
-      </c>
-      <c r="I13" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="J13" s="7">
-        <v>160</v>
-      </c>
-      <c r="K13" s="7">
-        <v>0.64</v>
-      </c>
-      <c r="L13" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="7">
-        <v>200</v>
-      </c>
-      <c r="E14" s="7">
-        <v>10</v>
-      </c>
-      <c r="F14" s="7">
-        <v>10</v>
-      </c>
-      <c r="G14" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="H14" s="7">
-        <v>60</v>
-      </c>
-      <c r="I14" s="7">
-        <v>3</v>
-      </c>
-      <c r="J14" s="7">
-        <v>170</v>
-      </c>
-      <c r="K14" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="L14" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="7">
-        <v>200</v>
-      </c>
-      <c r="E15" s="7">
-        <v>10</v>
-      </c>
-      <c r="F15" s="7">
-        <v>10</v>
-      </c>
-      <c r="G15" s="7">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
-        <v>60</v>
-      </c>
-      <c r="I15" s="7">
-        <v>3</v>
-      </c>
-      <c r="J15" s="7">
-        <v>170</v>
-      </c>
-      <c r="K15" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="L15" s="7">
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="7">
-        <v>320</v>
-      </c>
-      <c r="E16" s="7">
-        <v>16</v>
-      </c>
-      <c r="F16" s="7">
-        <v>16</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H16" s="7">
-        <v>112</v>
-      </c>
-      <c r="I16" s="7">
-        <v>4.8</v>
-      </c>
-      <c r="J16" s="7">
-        <v>312</v>
-      </c>
-      <c r="K16" s="7">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L16" s="7">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="7">
-        <v>500</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7">
-        <v>53.8</v>
-      </c>
-      <c r="G17" s="7">
-        <v>0.4</v>
-      </c>
-      <c r="H17" s="7">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7">
-        <v>0</v>
-      </c>
-      <c r="K17" s="7">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="7">
-        <v>150</v>
-      </c>
-      <c r="E18" s="7">
-        <v>5.6</v>
-      </c>
-      <c r="F18" s="7">
-        <v>5.8</v>
-      </c>
-      <c r="G18" s="7">
-        <v>150</v>
-      </c>
-      <c r="H18" s="7">
-        <v>100</v>
-      </c>
-      <c r="I18" s="7">
-        <v>1.45</v>
-      </c>
-      <c r="J18" s="7">
-        <v>200</v>
-      </c>
-      <c r="K18" s="7">
-        <v>0.37</v>
-      </c>
-      <c r="L18" s="7">
-        <v>4.8499999999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="7">
-        <v>150</v>
-      </c>
-      <c r="E19" s="7">
-        <v>5.6</v>
-      </c>
-      <c r="F19" s="7">
-        <v>5.8</v>
-      </c>
-      <c r="G19" s="7">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7">
-        <v>100</v>
-      </c>
-      <c r="I19" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="J19" s="7">
-        <v>200</v>
-      </c>
-      <c r="K19" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="L19" s="7">
-        <v>4.8499999999999996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="7">
-        <v>130</v>
-      </c>
-      <c r="E20" s="7">
-        <v>4</v>
-      </c>
-      <c r="F20" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="G20" s="7">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7">
-        <v>75</v>
-      </c>
-      <c r="I20" s="7">
-        <v>1.33</v>
-      </c>
-      <c r="J20" s="7">
-        <v>120</v>
-      </c>
-      <c r="K20" s="7">
-        <v>0.27</v>
-      </c>
-      <c r="L20" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="7">
-        <v>150</v>
-      </c>
-      <c r="E21" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="F21" s="7">
-        <v>5.8</v>
-      </c>
-      <c r="G21" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="H21" s="7">
-        <v>95</v>
-      </c>
-      <c r="I21" s="7">
-        <v>1.33</v>
-      </c>
-      <c r="J21" s="7">
-        <v>234</v>
-      </c>
-      <c r="K21" s="7">
-        <v>0.27</v>
-      </c>
-      <c r="L21" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="7">
-        <v>150</v>
-      </c>
-      <c r="E22" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="F22" s="7">
-        <v>5.8</v>
-      </c>
-      <c r="G22" s="7">
-        <v>0</v>
-      </c>
-      <c r="H22" s="7">
-        <v>120</v>
-      </c>
-      <c r="I22" s="7">
-        <v>1.33</v>
-      </c>
-      <c r="J22" s="7">
-        <v>234</v>
-      </c>
-      <c r="K22" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="L22" s="7">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="7">
-        <v>150</v>
-      </c>
-      <c r="E23" s="7">
-        <v>4</v>
-      </c>
-      <c r="F23" s="7">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7">
-        <v>0</v>
-      </c>
-      <c r="H23" s="7">
-        <v>6</v>
-      </c>
-      <c r="I23" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="J23" s="7">
-        <v>7</v>
-      </c>
-      <c r="K23" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="L23" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="7">
-        <v>200</v>
-      </c>
-      <c r="E24" s="7">
-        <v>3</v>
-      </c>
-      <c r="F24" s="7">
-        <v>8.9</v>
-      </c>
-      <c r="G24" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="H24" s="7">
-        <v>68</v>
-      </c>
-      <c r="I24" s="7">
-        <v>2</v>
-      </c>
-      <c r="J24" s="7">
-        <v>100</v>
-      </c>
-      <c r="K24" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="L24" s="7">
-        <v>6.67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="7">
-        <v>150</v>
-      </c>
-      <c r="E25" s="7">
-        <v>10</v>
-      </c>
-      <c r="F25" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="G25" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H25" s="7">
-        <v>58</v>
-      </c>
-      <c r="I25" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="J25" s="7">
-        <v>146</v>
-      </c>
-      <c r="K25" s="7">
-        <v>1</v>
-      </c>
-      <c r="L25" s="7">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="7">
-        <v>360</v>
-      </c>
-      <c r="E26" s="7">
-        <v>87</v>
-      </c>
-      <c r="F26" s="7">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0</v>
-      </c>
-      <c r="H26" s="7">
-        <v>550</v>
-      </c>
-      <c r="I26" s="7">
-        <v>0</v>
-      </c>
-      <c r="J26" s="7">
-        <v>1200</v>
-      </c>
-      <c r="K26" s="7">
-        <v>0</v>
-      </c>
-      <c r="L26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="7">
-        <v>150</v>
-      </c>
-      <c r="E27" s="7">
-        <v>10</v>
-      </c>
-      <c r="F27" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="G27" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="H27" s="7">
-        <v>47.5</v>
-      </c>
-      <c r="I27" s="7">
-        <v>0</v>
-      </c>
-      <c r="J27" s="7">
-        <v>128</v>
-      </c>
-      <c r="K27" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="L27" s="7">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="7">
-        <v>150</v>
-      </c>
-      <c r="E28" s="7">
-        <v>10</v>
-      </c>
-      <c r="F28" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="G28" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="H28" s="7">
-        <v>50</v>
-      </c>
-      <c r="I28" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="J28" s="7">
-        <v>146</v>
-      </c>
-      <c r="K28" s="7">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L28" s="7">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="7">
-        <v>100</v>
-      </c>
-      <c r="E29" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="F29" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="G29" s="7">
-        <v>0</v>
-      </c>
-      <c r="H29" s="7">
-        <v>80</v>
-      </c>
-      <c r="I29" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="J29" s="7">
-        <v>200</v>
-      </c>
-      <c r="K29" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="L29" s="7">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="7">
-        <v>100</v>
-      </c>
-      <c r="E30" s="7">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="F30" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="G30" s="7">
-        <v>0</v>
-      </c>
-      <c r="H30" s="7">
-        <v>80</v>
-      </c>
-      <c r="I30" s="7">
-        <v>1.3</v>
-      </c>
-      <c r="J30" s="7">
-        <v>200</v>
-      </c>
-      <c r="K30" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="L30" s="7">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="7">
-        <v>133</v>
-      </c>
-      <c r="E31" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="F31" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="G31" s="7">
-        <v>0</v>
-      </c>
-      <c r="H31" s="7">
-        <v>135</v>
-      </c>
-      <c r="I31" s="7">
-        <v>2</v>
-      </c>
-      <c r="J31" s="7">
-        <v>260</v>
-      </c>
-      <c r="K31" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="L31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="7">
-        <v>373</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7">
-        <v>0</v>
-      </c>
-      <c r="H32" s="7">
-        <v>174</v>
-      </c>
-      <c r="I32" s="7">
-        <v>0</v>
-      </c>
-      <c r="J32" s="7">
-        <v>0</v>
-      </c>
-      <c r="K32" s="7">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="7">
-        <v>291.10000000000002</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0</v>
-      </c>
-      <c r="F33" s="7">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7">
-        <v>31.2</v>
-      </c>
-      <c r="H33" s="7">
-        <v>1344</v>
-      </c>
-      <c r="I33" s="7">
-        <v>0</v>
-      </c>
-      <c r="J33" s="7">
-        <v>449</v>
-      </c>
-      <c r="K33" s="7">
-        <v>0</v>
-      </c>
-      <c r="L33" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="7">
-        <v>240</v>
-      </c>
-      <c r="E34" s="7">
-        <v>14.4</v>
-      </c>
-      <c r="F34" s="7">
-        <v>9.4</v>
-      </c>
-      <c r="G34" s="7">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7">
-        <v>30</v>
-      </c>
-      <c r="I34" s="7">
-        <v>2</v>
-      </c>
-      <c r="J34" s="7">
-        <v>87</v>
-      </c>
-      <c r="K34" s="7">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L34" s="7">
+      <c r="L34">
         <v>0.72</v>
       </c>
     </row>

--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfsoa\Desktop\Apps\db_nutribody\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25AC8A36-0D11-407E-BA87-C537D6EBBE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E82CBEC-CC53-47BD-B7C4-15113F928C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="2" xr2:uid="{334EDE72-1191-41F7-AA76-F0137DE60740}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{334EDE72-1191-41F7-AA76-F0137DE60740}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODIET" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="196">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -210,21 +210,12 @@
     <t>VIT.B12 (mcg)</t>
   </si>
   <si>
-    <t>TROPHIC BASIC</t>
-  </si>
-  <si>
-    <t>TROPHIC EP</t>
-  </si>
-  <si>
     <t>TROPHIC FIBER</t>
   </si>
   <si>
     <t>TROPHIC SOYA</t>
   </si>
   <si>
-    <t>TROPHIC SOYA 1.5</t>
-  </si>
-  <si>
     <t>ENEERGYZIP 1.5</t>
   </si>
   <si>
@@ -300,12 +291,6 @@
     <t>SACHE 10G</t>
   </si>
   <si>
-    <t>TROPHIC 1.5 FIBER (SF)</t>
-  </si>
-  <si>
-    <t>TROPHIC PROTEIN (SF)</t>
-  </si>
-  <si>
     <t>ENERGYZIP PROTEIN</t>
   </si>
   <si>
@@ -537,18 +522,12 @@
     <t>126G</t>
   </si>
   <si>
-    <t>TROPHIC 1.5 RTH</t>
-  </si>
-  <si>
     <t xml:space="preserve">1000ML </t>
   </si>
   <si>
     <t>APRESENTAÇÃO</t>
   </si>
   <si>
-    <t>TROPHIC 1.5</t>
-  </si>
-  <si>
     <t>1.000ML</t>
   </si>
   <si>
@@ -561,9 +540,6 @@
     <t>250ML</t>
   </si>
   <si>
-    <t>TROPHIC BASIC RTH</t>
-  </si>
-  <si>
     <t>800G</t>
   </si>
   <si>
@@ -579,9 +555,6 @@
     <t>2,07KG</t>
   </si>
   <si>
-    <t xml:space="preserve">TROPHIC 1.5 FIBER </t>
-  </si>
-  <si>
     <t>370G</t>
   </si>
   <si>
@@ -601,6 +574,48 @@
   </si>
   <si>
     <t xml:space="preserve">300G </t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5 250 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5 FIBER  1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5 FIBER  250 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5 RTH 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5 FIBER (SF) 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC SOYA 1.5 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC BASIC RTH 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC BASIC 800g</t>
+  </si>
+  <si>
+    <t>TROPHIC BASIC 400g</t>
+  </si>
+  <si>
+    <t>TROPHIC BASIC 2,07kg</t>
+  </si>
+  <si>
+    <t>TROPHIC BASIC 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC PROTEIN (SF) 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC EP 1000 mL</t>
   </si>
 </sst>
 </file>
@@ -1034,18 +1049,18 @@
         <v>59</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -1078,15 +1093,15 @@
         <v>0.8</v>
       </c>
       <c r="M2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1119,15 +1134,15 @@
         <v>0.8</v>
       </c>
       <c r="M3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1160,12 +1175,12 @@
         <v>0.8</v>
       </c>
       <c r="M4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1201,12 +1216,12 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1242,15 +1257,15 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1283,12 +1298,12 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1324,12 +1339,12 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1365,18 +1380,18 @@
         <v>0.6</v>
       </c>
       <c r="M9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D10">
         <v>435</v>
@@ -1406,15 +1421,15 @@
         <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -1447,15 +1462,15 @@
         <v>2</v>
       </c>
       <c r="M11" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -1488,15 +1503,15 @@
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1529,12 +1544,12 @@
         <v>0.6</v>
       </c>
       <c r="M13" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1570,12 +1585,12 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1611,12 +1626,12 @@
         <v>1.4</v>
       </c>
       <c r="M15" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1652,12 +1667,12 @@
         <v>0.5</v>
       </c>
       <c r="M16" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -1693,15 +1708,15 @@
         <v>0.5</v>
       </c>
       <c r="M17" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
@@ -1734,15 +1749,15 @@
         <v>0.5</v>
       </c>
       <c r="M18" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
@@ -1775,12 +1790,12 @@
         <v>0.5</v>
       </c>
       <c r="M19" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1816,12 +1831,12 @@
         <v>0.4</v>
       </c>
       <c r="M20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -1857,15 +1872,15 @@
         <v>0.4</v>
       </c>
       <c r="M21" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -1898,15 +1913,15 @@
         <v>0.4</v>
       </c>
       <c r="M22" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1939,12 +1954,12 @@
         <v>0.4</v>
       </c>
       <c r="M23" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -1980,12 +1995,12 @@
         <v>0.7</v>
       </c>
       <c r="M24" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -2021,12 +2036,12 @@
         <v>2</v>
       </c>
       <c r="M25" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -2062,15 +2077,15 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="M26" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -2103,15 +2118,15 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="M27" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
@@ -2144,15 +2159,15 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="M28" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
         <v>39</v>
@@ -2185,15 +2200,15 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="M29" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -2226,15 +2241,15 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -2267,18 +2282,18 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <v>199.97</v>
@@ -2308,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -2349,15 +2364,15 @@
         <v>1.6</v>
       </c>
       <c r="M33" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -2390,12 +2405,12 @@
         <v>1.6</v>
       </c>
       <c r="M34" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2431,12 +2446,12 @@
         <v>0.5</v>
       </c>
       <c r="M35" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -2472,15 +2487,15 @@
         <v>0.5</v>
       </c>
       <c r="M36" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
         <v>39</v>
@@ -2513,15 +2528,15 @@
         <v>9.4</v>
       </c>
       <c r="M37" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C38" t="s">
         <v>39</v>
@@ -2554,12 +2569,12 @@
         <v>9.4</v>
       </c>
       <c r="M38" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -2595,12 +2610,12 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="M39" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
         <v>3</v>
@@ -2636,12 +2651,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="M40" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
@@ -2677,15 +2692,15 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -2718,15 +2733,15 @@
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -2759,12 +2774,12 @@
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -2800,18 +2815,18 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2841,24 +2856,24 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D46">
         <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F46">
         <v>0.72</v>
@@ -2882,15 +2897,15 @@
         <v>0.48</v>
       </c>
       <c r="M46" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2923,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2981,7 +2996,7 @@
         <v>6</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3290,7 +3305,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -3404,7 +3419,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -3442,7 +3457,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -4215,12 +4230,12 @@
         <v>59</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
@@ -4258,7 +4273,7 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -4296,10 +4311,10 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4334,7 +4349,7 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -4372,7 +4387,7 @@
     </row>
     <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -4410,7 +4425,7 @@
     </row>
     <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -4448,7 +4463,7 @@
     </row>
     <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -4486,7 +4501,7 @@
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -4524,7 +4539,7 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -4562,7 +4577,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -4597,7 +4612,7 @@
     </row>
     <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -4635,7 +4650,7 @@
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -4673,7 +4688,7 @@
     </row>
     <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -4711,10 +4726,10 @@
     </row>
     <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -4749,10 +4764,10 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
@@ -4787,10 +4802,10 @@
     </row>
     <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
@@ -4825,13 +4840,13 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D18">
         <v>111</v>
@@ -4863,7 +4878,7 @@
     </row>
     <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -4901,7 +4916,7 @@
     </row>
     <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -4939,7 +4954,7 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -4977,13 +4992,13 @@
     </row>
     <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D22">
         <v>42</v>
@@ -5018,7 +5033,7 @@
         <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D23">
         <v>56</v>
@@ -5053,7 +5068,7 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D24">
         <v>70</v>
@@ -5139,15 +5154,15 @@
         <v>59</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>15</v>
@@ -5182,7 +5197,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -5220,7 +5235,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -5258,7 +5273,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -5293,7 +5308,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -5331,7 +5346,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -5369,7 +5384,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
@@ -5407,7 +5422,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -5445,7 +5460,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -5483,10 +5498,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -5521,7 +5536,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -5559,7 +5574,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -5597,7 +5612,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B14" t="s">
         <v>41</v>
@@ -5635,7 +5650,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B15" t="s">
         <v>41</v>
@@ -5673,10 +5688,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -5711,10 +5726,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -5749,7 +5764,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -5787,7 +5802,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -5825,7 +5840,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s">
         <v>41</v>
@@ -5863,7 +5878,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -5901,7 +5916,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
@@ -5939,7 +5954,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -5977,7 +5992,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -6015,7 +6030,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -6053,10 +6068,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -6091,7 +6106,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
@@ -6129,7 +6144,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -6167,7 +6182,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -6205,10 +6220,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
@@ -6243,10 +6258,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -6281,10 +6296,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
@@ -6319,10 +6334,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -6357,7 +6372,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>

--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfsoa\Desktop\Apps\db_nutribody\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E82CBEC-CC53-47BD-B7C4-15113F928C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2621BE-4446-48F8-8B16-753A811B502C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{334EDE72-1191-41F7-AA76-F0137DE60740}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="3" xr2:uid="{334EDE72-1191-41F7-AA76-F0137DE60740}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODIET" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="210">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -117,9 +117,6 @@
     <t>NUTREN 2.0</t>
   </si>
   <si>
-    <t>NUTREN CONTROL</t>
-  </si>
-  <si>
     <t>380G</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>15G</t>
   </si>
   <si>
-    <t>NUTREN SENIOR</t>
-  </si>
-  <si>
     <t>370G/740G</t>
   </si>
   <si>
@@ -210,90 +204,33 @@
     <t>VIT.B12 (mcg)</t>
   </si>
   <si>
-    <t>TROPHIC FIBER</t>
-  </si>
-  <si>
-    <t>TROPHIC SOYA</t>
-  </si>
-  <si>
-    <t>ENEERGYZIP 1.5</t>
-  </si>
-  <si>
-    <t>TROPHIC JUNIOR</t>
-  </si>
-  <si>
-    <t>ENERGYZIP SENIOR</t>
-  </si>
-  <si>
     <t>300G/SACHE 15G</t>
   </si>
   <si>
-    <t>BEMMAX</t>
-  </si>
-  <si>
     <t>350G</t>
   </si>
   <si>
     <t>52G</t>
   </si>
   <si>
-    <t>IMMAX</t>
-  </si>
-  <si>
     <t>350/700G</t>
   </si>
   <si>
-    <t>PROTEIN PT WHEY</t>
-  </si>
-  <si>
     <t>240G</t>
   </si>
   <si>
-    <t>PROTEIN PT CASEINATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAMAX IG </t>
-  </si>
-  <si>
-    <t>DIAMAX IN</t>
-  </si>
-  <si>
-    <t>HDMAX</t>
-  </si>
-  <si>
-    <t>PEPTIMAX</t>
-  </si>
-  <si>
-    <t>ENTERFIBER (FIBRAS SOLUVEIS E INSOLÚVEIS)</t>
-  </si>
-  <si>
     <t>SACHÊ 5G</t>
   </si>
   <si>
-    <t>ENTERFIBER PREBIOTIC (FIBRAS SOLUVEIS)</t>
-  </si>
-  <si>
-    <t>CARBO CH</t>
-  </si>
-  <si>
-    <t>ENERGYZIP SUSLAC</t>
-  </si>
-  <si>
     <t>60G</t>
   </si>
   <si>
     <t>5G</t>
   </si>
   <si>
-    <t>CORRECTMAX</t>
-  </si>
-  <si>
     <t>SACHE 10G</t>
   </si>
   <si>
-    <t>ENERGYZIP PROTEIN</t>
-  </si>
-  <si>
     <t>CALOGEN</t>
   </si>
   <si>
@@ -384,12 +321,6 @@
     <t>NOVASOURCE GC 1.5</t>
   </si>
   <si>
-    <t>NOVASOURCE REN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOVASOURCE REN </t>
-  </si>
-  <si>
     <t>1G</t>
   </si>
   <si>
@@ -570,9 +501,6 @@
     <t>25G</t>
   </si>
   <si>
-    <t xml:space="preserve">INSTANTH CLEAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">300G </t>
   </si>
   <si>
@@ -616,6 +544,120 @@
   </si>
   <si>
     <t>TROPHIC EP 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC FIBER 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC FIBER 400g</t>
+  </si>
+  <si>
+    <t>TROPHIC FIBER 800g</t>
+  </si>
+  <si>
+    <t>TROPHIC FIBER 2,07kg</t>
+  </si>
+  <si>
+    <t>TROPHIC SOYA 1000 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC SOYA 400g</t>
+  </si>
+  <si>
+    <t>TROPHIC SOYA 800g</t>
+  </si>
+  <si>
+    <t>TROPHIC SOYA 2,07kg</t>
+  </si>
+  <si>
+    <t>ENEERGYZIP 1.5 200 mL</t>
+  </si>
+  <si>
+    <t>ENERGYZIP PROTEIN 200 mL</t>
+  </si>
+  <si>
+    <t>TROPHIC JUNIOR 400g</t>
+  </si>
+  <si>
+    <t>TROPHIC JUNIOR 800g</t>
+  </si>
+  <si>
+    <t>ENERGYZIP SENIOR 370g</t>
+  </si>
+  <si>
+    <t>ENERGYZIP SENIOR 740g</t>
+  </si>
+  <si>
+    <t>PROTEIN PT WHEY 300g/sache 15g</t>
+  </si>
+  <si>
+    <t>PROTEIN PT CASEINATO 240g</t>
+  </si>
+  <si>
+    <t>BEMMAX 350g</t>
+  </si>
+  <si>
+    <t>IMMAX 350g</t>
+  </si>
+  <si>
+    <t>IMMAX 700g</t>
+  </si>
+  <si>
+    <t>DIAMAX IG  1000 mL</t>
+  </si>
+  <si>
+    <t>DIAMAX IG  200 mL</t>
+  </si>
+  <si>
+    <t>DIAMAX IN 370g</t>
+  </si>
+  <si>
+    <t>DIAMAX IN 740g</t>
+  </si>
+  <si>
+    <t>HDMAX 200 mL</t>
+  </si>
+  <si>
+    <t>PEPTIMAX 400g</t>
+  </si>
+  <si>
+    <t>ENTERFIBER (FIBRAS SOLUVEIS E INSOLÚVEIS) 400g</t>
+  </si>
+  <si>
+    <t>ENTERFIBER PREBIOTIC (FIBRAS SOLUVEIS) sache 5g</t>
+  </si>
+  <si>
+    <t>CARBO CH 25g</t>
+  </si>
+  <si>
+    <t>CARBO CH 400g</t>
+  </si>
+  <si>
+    <t>INSTANTH CLEAR 300g</t>
+  </si>
+  <si>
+    <t>ENERGYZIP SUSLAC 400g</t>
+  </si>
+  <si>
+    <t>CORRECTMAX sache 10g</t>
+  </si>
+  <si>
+    <t>NOVASOURCE REN 200 mL</t>
+  </si>
+  <si>
+    <t>NOVASOURCE REN  1000 mL</t>
+  </si>
+  <si>
+    <t>NUTREN CONTROL 200 mL</t>
+  </si>
+  <si>
+    <t>NUTREN CONTROL 360g</t>
+  </si>
+  <si>
+    <t>NUTREN SENIOR 200 mL</t>
+  </si>
+  <si>
+    <t>NUTREN SENIOR 370g /740g</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -1046,21 +1088,21 @@
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -1093,15 +1135,15 @@
         <v>0.8</v>
       </c>
       <c r="M2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1134,15 +1176,15 @@
         <v>0.8</v>
       </c>
       <c r="M3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1175,12 +1217,12 @@
         <v>0.8</v>
       </c>
       <c r="M4" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1216,12 +1258,12 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1257,15 +1299,15 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1298,12 +1340,12 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1339,12 +1381,12 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1380,18 +1422,18 @@
         <v>0.6</v>
       </c>
       <c r="M9" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="D10">
         <v>435</v>
@@ -1421,15 +1463,15 @@
         <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -1462,15 +1504,15 @@
         <v>2</v>
       </c>
       <c r="M11" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -1503,15 +1545,15 @@
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1544,12 +1586,12 @@
         <v>0.6</v>
       </c>
       <c r="M13" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1585,12 +1627,12 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1626,12 +1668,12 @@
         <v>1.4</v>
       </c>
       <c r="M15" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1667,12 +1709,12 @@
         <v>0.5</v>
       </c>
       <c r="M16" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -1708,15 +1750,15 @@
         <v>0.5</v>
       </c>
       <c r="M17" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="B18" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
@@ -1749,15 +1791,15 @@
         <v>0.5</v>
       </c>
       <c r="M18" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
@@ -1790,12 +1832,12 @@
         <v>0.5</v>
       </c>
       <c r="M19" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1831,12 +1873,12 @@
         <v>0.4</v>
       </c>
       <c r="M20" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -1872,15 +1914,15 @@
         <v>0.4</v>
       </c>
       <c r="M21" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -1913,15 +1955,15 @@
         <v>0.4</v>
       </c>
       <c r="M22" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1954,12 +1996,12 @@
         <v>0.4</v>
       </c>
       <c r="M23" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -1995,12 +2037,12 @@
         <v>0.7</v>
       </c>
       <c r="M24" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -2036,12 +2078,12 @@
         <v>2</v>
       </c>
       <c r="M25" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -2077,15 +2119,15 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="M26" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -2118,18 +2160,18 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="M27" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>184</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D28">
         <v>222</v>
@@ -2159,18 +2201,18 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="M28" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D29">
         <v>222</v>
@@ -2200,15 +2242,15 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="M29" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -2241,15 +2283,15 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -2282,18 +2324,18 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D32">
         <v>199.97</v>
@@ -2323,15 +2365,15 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -2364,15 +2406,15 @@
         <v>1.6</v>
       </c>
       <c r="M33" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="B34" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -2405,12 +2447,12 @@
         <v>1.6</v>
       </c>
       <c r="M34" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2446,12 +2488,12 @@
         <v>0.5</v>
       </c>
       <c r="M35" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -2487,18 +2529,18 @@
         <v>0.5</v>
       </c>
       <c r="M36" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D37">
         <v>239</v>
@@ -2528,18 +2570,18 @@
         <v>9.4</v>
       </c>
       <c r="M37" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D38">
         <v>239</v>
@@ -2569,12 +2611,12 @@
         <v>9.4</v>
       </c>
       <c r="M38" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -2610,12 +2652,12 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="M39" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s">
         <v>3</v>
@@ -2651,12 +2693,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="M40" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
@@ -2692,15 +2734,15 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -2733,15 +2775,15 @@
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -2774,12 +2816,12 @@
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -2815,18 +2857,18 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2856,24 +2898,24 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D46">
         <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F46">
         <v>0.72</v>
@@ -2897,15 +2939,15 @@
         <v>0.48</v>
       </c>
       <c r="M46" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2938,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2966,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -2996,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3305,7 +3347,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -3419,7 +3461,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -3457,7 +3499,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -3647,7 +3689,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -3685,13 +3727,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>30</v>
-      </c>
-      <c r="C20" t="s">
-        <v>31</v>
       </c>
       <c r="D20">
         <v>88</v>
@@ -3723,13 +3765,13 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
       </c>
       <c r="D21">
         <v>132</v>
@@ -3761,13 +3803,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
         <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
       </c>
       <c r="D22">
         <v>52</v>
@@ -3796,7 +3838,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -3834,13 +3876,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
         <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
       </c>
       <c r="D24">
         <v>236</v>
@@ -3872,10 +3914,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -3910,7 +3952,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -3948,7 +3990,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -3986,7 +4028,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -4024,13 +4066,13 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4062,13 +4104,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D30">
         <v>7.3</v>
@@ -4100,13 +4142,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D31">
         <v>11</v>
@@ -4138,13 +4180,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D32">
         <v>16</v>
@@ -4200,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -4227,15 +4269,15 @@
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
@@ -4273,7 +4315,7 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -4311,10 +4353,10 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4349,7 +4391,7 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -4387,7 +4429,7 @@
     </row>
     <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -4425,7 +4467,7 @@
     </row>
     <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -4463,7 +4505,7 @@
     </row>
     <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -4501,10 +4543,10 @@
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -4539,7 +4581,7 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -4577,7 +4619,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -4612,7 +4654,7 @@
     </row>
     <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -4650,7 +4692,7 @@
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -4688,7 +4730,7 @@
     </row>
     <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -4726,10 +4768,10 @@
     </row>
     <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -4764,10 +4806,10 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
@@ -4802,10 +4844,10 @@
     </row>
     <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
@@ -4840,13 +4882,13 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D18">
         <v>111</v>
@@ -4878,7 +4920,7 @@
     </row>
     <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -4916,7 +4958,7 @@
     </row>
     <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -4954,7 +4996,7 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -4992,13 +5034,13 @@
     </row>
     <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D22">
         <v>42</v>
@@ -5030,10 +5072,10 @@
     </row>
     <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D23">
         <v>56</v>
@@ -5065,10 +5107,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D24">
         <v>70</v>
@@ -5124,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -5151,18 +5193,18 @@
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>15</v>
@@ -5197,7 +5239,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -5235,7 +5277,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -5273,7 +5315,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -5308,7 +5350,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -5346,7 +5388,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -5384,10 +5426,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -5422,10 +5464,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -5460,7 +5502,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -5498,10 +5540,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -5536,7 +5578,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -5574,7 +5616,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -5612,10 +5654,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -5650,10 +5692,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -5688,10 +5730,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -5726,10 +5768,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -5764,7 +5806,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -5802,7 +5844,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -5840,10 +5882,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -5878,7 +5920,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -5916,10 +5958,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
@@ -5954,7 +5996,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -5992,7 +6034,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -6030,7 +6072,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -6068,10 +6110,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -6106,10 +6148,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
@@ -6144,7 +6186,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -6182,7 +6224,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -6220,10 +6262,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
@@ -6258,10 +6300,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -6296,10 +6338,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
@@ -6334,10 +6376,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -6372,7 +6414,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
